--- a/Data/g1.3.xlsx
+++ b/Data/g1.3.xlsx
@@ -457,14 +457,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>106255.6657838777</v>
+        <v>118174.1116095417</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>PIB 2022 Deflacionado</t>
+          <t>PIB 2023 Deflacionado</t>
         </is>
       </c>
     </row>
@@ -475,14 +475,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>71631.77332808671</v>
+        <v>76532.28963539573</v>
       </c>
       <c r="C3" t="n">
         <v>2</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PIB 2022 Deflacionado</t>
+          <t>PIB 2023 Deflacionado</t>
         </is>
       </c>
     </row>
@@ -493,50 +493,50 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>67103.78239198164</v>
+        <v>73845.19036585005</v>
       </c>
       <c r="C4" t="n">
         <v>3</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PIB 2022 Deflacionado</t>
+          <t>PIB 2023 Deflacionado</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>66053.31857417851</v>
+        <v>69959.10090505773</v>
       </c>
       <c r="C5" t="n">
         <v>4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PIB 2022 Deflacionado</t>
+          <t>PIB 2023 Deflacionado</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RJ</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>63538.30060720995</v>
+        <v>67161.88535005336</v>
       </c>
       <c r="C6" t="n">
         <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PIB 2022 Deflacionado</t>
+          <t>PIB 2023 Deflacionado</t>
         </is>
       </c>
     </row>
@@ -547,14 +547,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>58610.8875231719</v>
+        <v>64948.89321994126</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PIB 2022 Deflacionado</t>
+          <t>PIB 2023 Deflacionado</t>
         </is>
       </c>
     </row>
@@ -565,14 +565,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24534.05142415514</v>
+        <v>26006.98661973922</v>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PIB 2022 Deflacionado</t>
+          <t>PIB 2023 Deflacionado</t>
         </is>
       </c>
     </row>
@@ -583,12 +583,12 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47251.95921644355</v>
+        <v>51300.70579350938</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PIB 2022 Deflacionado</t>
+          <t>PIB 2023 Deflacionado</t>
         </is>
       </c>
     </row>
@@ -599,48 +599,48 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24069.74856943695</v>
+        <v>26237.41536180414</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PIB 2022 Deflacionado</t>
+          <t>PIB 2023 Deflacionado</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>PI</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.480568130444567</v>
+        <v>1.537570136346218</v>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Variação (%) 2022/2010</t>
+          <t>Variação (%) 2023/2010</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.354725492322902</v>
+        <v>1.47614098883597</v>
       </c>
       <c r="C12" t="n">
         <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Variação (%) 2022/2010</t>
+          <t>Variação (%) 2023/2010</t>
         </is>
       </c>
     </row>
@@ -651,68 +651,68 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.34745626151513</v>
+        <v>1.456636142415122</v>
       </c>
       <c r="C13" t="n">
         <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Variação (%) 2022/2010</t>
+          <t>Variação (%) 2023/2010</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.329885262395931</v>
+        <v>1.361548723808843</v>
       </c>
       <c r="C14" t="n">
         <v>4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Variação (%) 2022/2010</t>
+          <t>Variação (%) 2023/2010</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.256546683333379</v>
+        <v>1.347864888435147</v>
       </c>
       <c r="C15" t="n">
         <v>5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Variação (%) 2022/2010</t>
+          <t>Variação (%) 2023/2010</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RJ</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.228221586781506</v>
+        <v>1.330588661237085</v>
       </c>
       <c r="C16" t="n">
         <v>6</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Variação (%) 2022/2010</t>
+          <t>Variação (%) 2023/2010</t>
         </is>
       </c>
     </row>
@@ -723,14 +723,14 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8656526888418142</v>
+        <v>0.91785810919599</v>
       </c>
       <c r="C17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Variação (%) 2022/2010</t>
+          <t>Variação (%) 2023/2010</t>
         </is>
       </c>
     </row>
@@ -741,12 +741,12 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.097514270052011</v>
+        <v>1.205735709293767</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Variação (%) 2022/2010</t>
+          <t>Variação (%) 2023/2010</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.168334463344599</v>
+        <v>1.297733510014661</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Variação (%) 2022/2010</t>
+          <t>Variação (%) 2023/2010</t>
         </is>
       </c>
     </row>
